--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541501</v>
       </c>
       <c r="B2" t="n">
-        <v>87011</v>
+        <v>87039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541501</v>
       </c>
       <c r="B2" t="n">
-        <v>87039</v>
+        <v>87045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541501</v>
       </c>
       <c r="B2" t="n">
-        <v>87045</v>
+        <v>87046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541501</v>
       </c>
       <c r="B2" t="n">
-        <v>87046</v>
+        <v>87051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541501</v>
       </c>
       <c r="B2" t="n">
-        <v>87051</v>
+        <v>87055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541501</v>
       </c>
       <c r="B2" t="n">
-        <v>87055</v>
+        <v>87057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541501</v>
       </c>
       <c r="B2" t="n">
-        <v>87057</v>
+        <v>87060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129541501</v>
+        <v>62417830</v>
       </c>
       <c r="B2" t="n">
-        <v>87060</v>
+        <v>87211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>248950</v>
+        <v>430</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Själlandsspindling</t>
+          <t>Blå lökspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius selandicus</t>
+          <t>Cortinarius caerulescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Frøslev &amp; T.S.Jeppesen</t>
+          <t>(Schaeff.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Myrestad, Sk</t>
+          <t>Myrestad, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443288</v>
+        <v>443214</v>
       </c>
       <c r="R2" t="n">
-        <v>6180031</v>
+        <v>6180226</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2016-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Exkursion Puggehatten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,22 +759,1514 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>bokskog i bäckravin</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Sigvard Svensson, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>96246912</v>
+      </c>
+      <c r="B3" t="n">
+        <v>87491</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>440</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Cinnoberspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius cinnabarinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Myrestad, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>443242</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6180226</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ädellövskog i ravin längs bäck.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tony Svensson, Anders Wånge Kjellsson, Charlotte Wigermo, Krister Wadén, Shu-Chin Hysing, Ulla Berglund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Puggehatten, exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106564607</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87248</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kejsarspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantissimus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Myrestad, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>443266</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6180230</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Luktar kräftspad</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sigvard Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sigvard Svensson, Charlotte Wigermo, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Puggehatten, exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128856480</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87248</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kejsarspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantissimus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Myrestad, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>443176</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6180189</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn, Mattias Andersson, Karin Hjelmér, Olle Amcoff, Anders Wånge Kjellsson, Oskar Karl Elias Olsson, Hans Rydberg, Martin Peraic, Margaux Boeraeve, Claes Ingvert, Cecilia  Wånge , Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128891669</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87248</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kejsarspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantissimus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Myrestad, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>443206</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6180223</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bok</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn, Mattias Andersson, Karin Hjelmér, Olle Amcoff, Anders Wånge Kjellsson, Oskar Karl Elias Olsson, Hans Rydberg, Martin Peraic, Margaux Boeraeve, Claes Ingvert, Cecilia  Wånge , Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>61983788</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87394</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>474</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rävspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius vulpinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Velen.) Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Myrestad, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>443183</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6180192</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-10-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-10-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 fruktkropp.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Bokskog, sluttning</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Örjan Fritz, Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>61983789</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87394</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>474</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rävspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius vulpinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Velen.) Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Myrestad, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>443191</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6180214</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-10-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-10-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 fruktkropp.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bokskog, sluttning</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz, Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>62416653</v>
+      </c>
+      <c r="B9" t="n">
+        <v>87394</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>474</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rävspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius vulpinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Velen.) Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Myrestad, 500 m OSO, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>443214</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6180226</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Exkursion Puggehatten</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Sigvard Svensson, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>62417831</v>
+      </c>
+      <c r="B10" t="n">
+        <v>88424</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1008</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Igelkottsröksvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycoperdon echinatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Myrestad, 500 m OSO, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>443214</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6180226</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Exkursion Puggehatten</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>bokskog i bäckravin</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Sigvard Svensson, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113793290</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75379</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stiftklotterlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Opegrapha vermicellifera</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Kunze) J.R.Laundon</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tingalycka, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>443195</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6180204</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-12-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-12-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113793305</v>
+      </c>
+      <c r="B12" t="n">
+        <v>77726</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bokvårtlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrenula nitida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tingalycka, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>443160</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6180189</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-12-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-12-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113793311</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97811</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2604</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trädporella</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porella platyphylla</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tingalycka, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>443160</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6180189</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-12-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-12-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>96246923</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87365</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3562</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nunnespindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius subalbescens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Reumaux</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Myrestad, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>443202</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6180215</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sporer tydligt mandelformade 9 x 5 um.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Ädellövskog i ravin längs bäck.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tony Svensson, Anders Wånge Kjellsson, Charlotte Wigermo, Krister Wadén, Shu-Chin Hysing, Ulla Berglund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Puggehatten, exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129541501</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87352</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>248950</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Själlandsspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius selandicus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; T.S.Jeppesen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Myrestad, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>443288</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6180031</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Sofia Lund</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Sofia Lund, Tony Svensson, Mats Karlsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62417830</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
           <t>Puggehatten, exkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96246912</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
           <t>Puggehatten, exkursion</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106564607</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
           <t>SMF:s mykologivecka</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128856480</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
           <t>SMF:s mykologivecka</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128891669</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1354,6 +1384,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61983788</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61983789</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62416653</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1690,6 +1735,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62417831</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113793290</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1922,6 +1977,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113793305</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2039,6 +2099,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113793311</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2164,6 +2229,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Puggehatten, exkursion</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96246923</t>
         </is>
       </c>
     </row>
@@ -2267,8 +2337,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129541501</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>